--- a/satisfaction_surveys/013_food_service_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/013_food_service_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'overpriced'}</t>
+          <t>overpriced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Overpriced'}</t>
+          <t>Overpriced</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'underpriced'}</t>
+          <t>underpriced</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Underpriced'}</t>
+          <t>Underpriced</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not applicable'}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'too_small'}</t>
+          <t>too_small</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Too small'}</t>
+          <t>Too small</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'too_large'}</t>
+          <t>too_large</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Too large'}</t>
+          <t>Too large</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not applicable'}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_attractive'}</t>
+          <t>not_attractive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not attractive'}</t>
+          <t>Not attractive</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'attractive'}</t>
+          <t>attractive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Attractive'}</t>
+          <t>Attractive</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not applicable'}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'not_friendly'}</t>
+          <t>not_friendly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Not friendly'}</t>
+          <t>Not friendly</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'friendly'}</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Friendly'}</t>
+          <t>Friendly</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not applicable'}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Satisfied'}</t>
+          <t>Extremely Satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_satisfied'}</t>
+          <t>extremely_satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Satisfied'}</t>
+          <t>Extremely Satisfied</t>
         </is>
       </c>
     </row>
